--- a/Ecobliss_Results.xlsx
+++ b/Ecobliss_Results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2025/Ghana_Project/SOC Modeling/RothC/RothC_Calibrated/RothC_Implementation_Ecobliss/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2025/Ghana_Project/QA1_&amp;_3/Code/RothC_Implementation_Ecobliss/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3866D415-0C5A-2F42-B596-F16F845FC9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F952E342-A943-A743-BA41-7472EF3CA462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{AA4B684E-F9E2-7F41-996C-BD2AB92E0EF7}"/>
   </bookViews>
@@ -18,9 +18,6 @@
     <sheet name="Project Model Error" sheetId="3" r:id="rId3"/>
     <sheet name="Sampling &amp; Combined Error" sheetId="4" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -64,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="248">
   <si>
     <t>Year</t>
   </si>
@@ -771,9 +768,6 @@
     <t>Baseline Sampling Error (tC/ha/yr)^2</t>
   </si>
   <si>
-    <t>Baseline Model Error (tC/ha/yr)^2</t>
-  </si>
-  <si>
     <t>Total Error (tC/ha/yr)^2</t>
   </si>
   <si>
@@ -781,6 +775,39 @@
   </si>
   <si>
     <t>Representative Area</t>
+  </si>
+  <si>
+    <t>Model Error (tC/ha/yr)^2</t>
+  </si>
+  <si>
+    <t>QA1</t>
+  </si>
+  <si>
+    <t>QA3</t>
+  </si>
+  <si>
+    <t>N2O Emissions Burning (Baseline only)</t>
+  </si>
+  <si>
+    <t>CH4 Emissions Burning (Baseline only)</t>
+  </si>
+  <si>
+    <t>Fossil Fuel (Baseline)</t>
+  </si>
+  <si>
+    <t>Fossil Fuel (Project)</t>
+  </si>
+  <si>
+    <t>Fertilizer Usage (Baseline)</t>
+  </si>
+  <si>
+    <t>Fertilizer Usage (Project)</t>
+  </si>
+  <si>
+    <t>Total (QA3 Emissions)</t>
+  </si>
+  <si>
+    <t>NPRT</t>
   </si>
 </sst>
 </file>
@@ -1114,7 +1141,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1391,11 +1418,14 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1413,34 +1443,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Net ERs"/>
-      <sheetName val="Baseline Model Error"/>
-      <sheetName val="Project Model Error"/>
-      <sheetName val="Sampling &amp; Combined Error"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="80">
-          <cell r="B80">
-            <v>0.41731085305615684</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1760,15 +1762,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8459C356-BFF7-1A4F-8872-7C39E98F0955}">
-  <dimension ref="A2:H19"/>
+  <dimension ref="A2:T19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
     <col min="6" max="6" width="13.1640625" customWidth="1"/>
     <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32.6640625" customWidth="1"/>
+    <col min="10" max="10" width="32.83203125" customWidth="1"/>
+    <col min="11" max="11" width="19.83203125" customWidth="1"/>
+    <col min="12" max="12" width="18.5" customWidth="1"/>
+    <col min="13" max="13" width="22.5" customWidth="1"/>
+    <col min="14" max="14" width="22.1640625" customWidth="1"/>
+    <col min="15" max="15" width="19.5" customWidth="1"/>
+    <col min="20" max="20" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1777,7 +1787,22 @@
         <v>18200</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="F3" s="125" t="s">
+        <v>238</v>
+      </c>
+      <c r="G3" s="125"/>
+      <c r="I3" s="125" t="s">
+        <v>239</v>
+      </c>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1797,11 +1822,36 @@
       <c r="G4" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="3"/>
+      <c r="I4" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="T4" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>220</v>
       </c>
@@ -1821,11 +1871,33 @@
       <c r="G5" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="1"/>
+      <c r="I5" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="J5" t="s">
+        <v>222</v>
+      </c>
+      <c r="K5" t="s">
+        <v>222</v>
+      </c>
+      <c r="L5" t="s">
+        <v>222</v>
+      </c>
+      <c r="M5" t="s">
+        <v>222</v>
+      </c>
+      <c r="N5" t="s">
+        <v>222</v>
+      </c>
+      <c r="O5" t="s">
+        <v>222</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1845,14 +1917,11 @@
       </c>
       <c r="G6">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
-        <v>39079.761084039063</v>
-      </c>
-      <c r="H6" s="124">
-        <f>F6-G6</f>
-        <v>492585.17338329431</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+        <v>39079.761084041042</v>
+      </c>
+      <c r="H6" s="123"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>2024</v>
       </c>
@@ -1872,14 +1941,37 @@
       </c>
       <c r="G7">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
-        <v>39079.761084039063</v>
-      </c>
-      <c r="H7" s="124">
-        <f t="shared" ref="H7:H18" si="2">F7-G7</f>
-        <v>473289.32147462759</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+        <v>39079.761084041042</v>
+      </c>
+      <c r="H7" s="123"/>
+      <c r="I7">
+        <v>217.375</v>
+      </c>
+      <c r="J7">
+        <v>379.66660000000002</v>
+      </c>
+      <c r="K7">
+        <v>1554.49771021999</v>
+      </c>
+      <c r="L7">
+        <v>1107.5355199999999</v>
+      </c>
+      <c r="M7">
+        <v>12306.966700000001</v>
+      </c>
+      <c r="N7">
+        <v>6153.4832999999999</v>
+      </c>
+      <c r="O7">
+        <f>(N7+L7)-(I7+J7+K7+M7)</f>
+        <v>-7197.487190219992</v>
+      </c>
+      <c r="T7" s="123">
+        <f>F7- G7 - O7</f>
+        <v>480486.80866484559</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>2025</v>
       </c>
@@ -1899,14 +1991,37 @@
       </c>
       <c r="G8">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
-        <v>39079.761084039063</v>
-      </c>
-      <c r="H8" s="124">
-        <f t="shared" si="2"/>
-        <v>458157.00694396102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+        <v>39079.761084041042</v>
+      </c>
+      <c r="H8" s="123"/>
+      <c r="I8">
+        <v>217.375</v>
+      </c>
+      <c r="J8">
+        <v>379.66660000000002</v>
+      </c>
+      <c r="K8">
+        <v>1554.49771021999</v>
+      </c>
+      <c r="L8">
+        <v>1107.5355199999999</v>
+      </c>
+      <c r="M8">
+        <v>12306.966700000001</v>
+      </c>
+      <c r="N8">
+        <v>6153.4832999999999</v>
+      </c>
+      <c r="O8">
+        <f t="shared" ref="O8:O18" si="2">(N8+L8)-(I8+J8+K8+M8)</f>
+        <v>-7197.487190219992</v>
+      </c>
+      <c r="T8" s="123">
+        <f>F8-G8 - O8</f>
+        <v>465354.49413417903</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>2026</v>
       </c>
@@ -1926,14 +2041,37 @@
       </c>
       <c r="G9">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
-        <v>39079.761084039063</v>
-      </c>
-      <c r="H9" s="124">
+        <v>39079.761084041042</v>
+      </c>
+      <c r="H9" s="123"/>
+      <c r="I9">
+        <v>217.375</v>
+      </c>
+      <c r="J9">
+        <v>379.66660000000002</v>
+      </c>
+      <c r="K9">
+        <v>1554.49771021999</v>
+      </c>
+      <c r="L9">
+        <v>1107.5355199999999</v>
+      </c>
+      <c r="M9">
+        <v>12306.966700000001</v>
+      </c>
+      <c r="N9">
+        <v>6153.4832999999999</v>
+      </c>
+      <c r="O9">
         <f t="shared" si="2"/>
-        <v>464736.56859929417</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+        <v>-7197.487190219992</v>
+      </c>
+      <c r="T9" s="123">
+        <f>F9-G9 - O9</f>
+        <v>471934.05578951217</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>2027</v>
       </c>
@@ -1953,14 +2091,37 @@
       </c>
       <c r="G10">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
-        <v>39079.761084039063</v>
-      </c>
-      <c r="H10" s="124">
+        <v>39079.761084041042</v>
+      </c>
+      <c r="H10" s="123"/>
+      <c r="I10">
+        <v>217.375</v>
+      </c>
+      <c r="J10">
+        <v>379.66660000000002</v>
+      </c>
+      <c r="K10">
+        <v>1554.49771021999</v>
+      </c>
+      <c r="L10">
+        <v>1107.5355199999999</v>
+      </c>
+      <c r="M10">
+        <v>12306.966700000001</v>
+      </c>
+      <c r="N10">
+        <v>6153.4832999999999</v>
+      </c>
+      <c r="O10">
         <f t="shared" si="2"/>
-        <v>469528.53377729421</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+        <v>-7197.487190219992</v>
+      </c>
+      <c r="T10" s="123">
+        <f>F10-G10 - O10</f>
+        <v>476726.02096751222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>2028</v>
       </c>
@@ -1980,14 +2141,37 @@
       </c>
       <c r="G11">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
-        <v>39079.761084039063</v>
-      </c>
-      <c r="H11" s="124">
+        <v>39079.761084041042</v>
+      </c>
+      <c r="H11" s="123"/>
+      <c r="I11">
+        <v>217.375</v>
+      </c>
+      <c r="J11">
+        <v>379.66660000000002</v>
+      </c>
+      <c r="K11">
+        <v>1554.49771021999</v>
+      </c>
+      <c r="L11">
+        <v>1107.5355199999999</v>
+      </c>
+      <c r="M11">
+        <v>12306.966700000001</v>
+      </c>
+      <c r="N11">
+        <v>6153.4832999999999</v>
+      </c>
+      <c r="O11">
         <f t="shared" si="2"/>
-        <v>473034.68242329441</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+        <v>-7197.487190219992</v>
+      </c>
+      <c r="T11" s="123">
+        <f>F11-G11 - O11</f>
+        <v>480232.16961351241</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>2029</v>
       </c>
@@ -2007,14 +2191,37 @@
       </c>
       <c r="G12">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
-        <v>39079.761084039063</v>
-      </c>
-      <c r="H12" s="124">
+        <v>39079.761084041042</v>
+      </c>
+      <c r="H12" s="123"/>
+      <c r="I12">
+        <v>217.375</v>
+      </c>
+      <c r="J12">
+        <v>379.66660000000002</v>
+      </c>
+      <c r="K12">
+        <v>1554.49771021999</v>
+      </c>
+      <c r="L12">
+        <v>1107.5355199999999</v>
+      </c>
+      <c r="M12">
+        <v>12306.966700000001</v>
+      </c>
+      <c r="N12">
+        <v>6153.4832999999999</v>
+      </c>
+      <c r="O12">
         <f t="shared" si="2"/>
-        <v>475614.84333996096</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+        <v>-7197.487190219992</v>
+      </c>
+      <c r="T12" s="123">
+        <f>F12-G12 - O12</f>
+        <v>482812.33053017897</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>2030</v>
       </c>
@@ -2034,14 +2241,37 @@
       </c>
       <c r="G13">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
-        <v>39079.761084039063</v>
-      </c>
-      <c r="H13" s="124">
+        <v>39079.761084041042</v>
+      </c>
+      <c r="H13" s="123"/>
+      <c r="I13">
+        <v>217.375</v>
+      </c>
+      <c r="J13">
+        <v>379.66660000000002</v>
+      </c>
+      <c r="K13">
+        <v>1554.49771021999</v>
+      </c>
+      <c r="L13">
+        <v>1107.5355199999999</v>
+      </c>
+      <c r="M13">
+        <v>12306.966700000001</v>
+      </c>
+      <c r="N13">
+        <v>6153.4832999999999</v>
+      </c>
+      <c r="O13">
         <f t="shared" si="2"/>
-        <v>477527.56815396098</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+        <v>-7197.487190219992</v>
+      </c>
+      <c r="T13" s="123">
+        <f>F13-G13 - O13</f>
+        <v>484725.05534417898</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>2031</v>
       </c>
@@ -2061,14 +2291,37 @@
       </c>
       <c r="G14">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
-        <v>39079.761084039063</v>
-      </c>
-      <c r="H14" s="124">
+        <v>39079.761084041042</v>
+      </c>
+      <c r="H14" s="123"/>
+      <c r="I14">
+        <v>217.375</v>
+      </c>
+      <c r="J14">
+        <v>379.66660000000002</v>
+      </c>
+      <c r="K14">
+        <v>1554.49771021999</v>
+      </c>
+      <c r="L14">
+        <v>1107.5355199999999</v>
+      </c>
+      <c r="M14">
+        <v>12306.966700000001</v>
+      </c>
+      <c r="N14">
+        <v>6153.4832999999999</v>
+      </c>
+      <c r="O14">
         <f t="shared" si="2"/>
-        <v>478958.78527462756</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+        <v>-7197.487190219992</v>
+      </c>
+      <c r="T14" s="123">
+        <f>F14-G14 - O14</f>
+        <v>486156.27246484556</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>2032</v>
       </c>
@@ -2088,14 +2341,37 @@
       </c>
       <c r="G15">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
-        <v>39079.761084039063</v>
-      </c>
-      <c r="H15" s="124">
+        <v>39079.761084041042</v>
+      </c>
+      <c r="H15" s="123"/>
+      <c r="I15">
+        <v>217.375</v>
+      </c>
+      <c r="J15">
+        <v>379.66660000000002</v>
+      </c>
+      <c r="K15">
+        <v>1554.49771021999</v>
+      </c>
+      <c r="L15">
+        <v>1107.5355199999999</v>
+      </c>
+      <c r="M15">
+        <v>12306.966700000001</v>
+      </c>
+      <c r="N15">
+        <v>6153.4832999999999</v>
+      </c>
+      <c r="O15">
         <f t="shared" si="2"/>
-        <v>480042.26300329436</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+        <v>-7197.487190219992</v>
+      </c>
+      <c r="T15" s="123">
+        <f>F15-G15 - O15</f>
+        <v>487239.75019351236</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>2033</v>
       </c>
@@ -2115,14 +2391,37 @@
       </c>
       <c r="G16">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
-        <v>39079.761084039063</v>
-      </c>
-      <c r="H16" s="124">
+        <v>39079.761084041042</v>
+      </c>
+      <c r="H16" s="123"/>
+      <c r="I16">
+        <v>217.375</v>
+      </c>
+      <c r="J16">
+        <v>379.66660000000002</v>
+      </c>
+      <c r="K16">
+        <v>1554.49771021999</v>
+      </c>
+      <c r="L16">
+        <v>1107.5355199999999</v>
+      </c>
+      <c r="M16">
+        <v>12306.966700000001</v>
+      </c>
+      <c r="N16">
+        <v>6153.4832999999999</v>
+      </c>
+      <c r="O16">
         <f t="shared" si="2"/>
-        <v>480874.31889462762</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+        <v>-7197.487190219992</v>
+      </c>
+      <c r="T16" s="123">
+        <f>F16-G16 - O16</f>
+        <v>488071.80608484562</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>2034</v>
       </c>
@@ -2142,14 +2441,37 @@
       </c>
       <c r="G17">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
-        <v>39079.761084039063</v>
-      </c>
-      <c r="H17" s="124">
+        <v>39079.761084041042</v>
+      </c>
+      <c r="H17" s="123"/>
+      <c r="I17">
+        <v>217.375</v>
+      </c>
+      <c r="J17">
+        <v>379.66660000000002</v>
+      </c>
+      <c r="K17">
+        <v>1554.49771021999</v>
+      </c>
+      <c r="L17">
+        <v>1107.5355199999999</v>
+      </c>
+      <c r="M17">
+        <v>12306.966700000001</v>
+      </c>
+      <c r="N17">
+        <v>6153.4832999999999</v>
+      </c>
+      <c r="O17">
         <f t="shared" si="2"/>
-        <v>481524.30689996097</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+        <v>-7197.487190219992</v>
+      </c>
+      <c r="T17" s="123">
+        <f>F17-G17 - O17</f>
+        <v>488721.79409017897</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>2035</v>
       </c>
@@ -2169,17 +2491,44 @@
       </c>
       <c r="G18">
         <f>SQRT('Sampling &amp; Combined Error'!$E$14)*$B$2*44/12</f>
-        <v>39079.761084039063</v>
-      </c>
-      <c r="H18" s="124">
+        <v>39079.761084041042</v>
+      </c>
+      <c r="H18" s="123"/>
+      <c r="I18">
+        <v>217.375</v>
+      </c>
+      <c r="J18">
+        <v>379.66660000000002</v>
+      </c>
+      <c r="K18">
+        <v>1554.49771021999</v>
+      </c>
+      <c r="L18">
+        <v>1107.5355199999999</v>
+      </c>
+      <c r="M18">
+        <v>12306.966700000001</v>
+      </c>
+      <c r="N18">
+        <v>6153.4832999999999</v>
+      </c>
+      <c r="O18">
         <f t="shared" si="2"/>
-        <v>482042.18359262764</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+        <v>-7197.487190219992</v>
+      </c>
+      <c r="T18" s="123">
+        <f>F18-G18 - O18</f>
+        <v>489239.67078284564</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="F19" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="I3:O3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11941,16 +12290,16 @@
       <c r="R85"/>
     </row>
     <row r="86" spans="1:44" ht="97" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="121" t="s">
+      <c r="B86" s="124" t="s">
         <v>218</v>
       </c>
-      <c r="C86" s="121"/>
-      <c r="D86" s="121"/>
-      <c r="E86" s="121"/>
-      <c r="F86" s="122"/>
-      <c r="G86" s="122"/>
-      <c r="H86" s="122"/>
-      <c r="I86" s="122"/>
+      <c r="C86" s="124"/>
+      <c r="D86" s="124"/>
+      <c r="E86" s="124"/>
+      <c r="F86" s="121"/>
+      <c r="G86" s="121"/>
+      <c r="H86" s="121"/>
+      <c r="I86" s="121"/>
       <c r="J86"/>
       <c r="K86"/>
       <c r="O86"/>
@@ -15196,7 +15545,7 @@
         <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C2" t="s">
         <v>225</v>
@@ -15259,7 +15608,7 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="D4:D5" si="0">4.20750878</f>
+        <f t="shared" ref="D4" si="0">4.20750878</f>
         <v>4.2075087800000004</v>
       </c>
       <c r="E4">
@@ -15279,7 +15628,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B9" s="3">
         <f>SUM(B3:B8)</f>
@@ -15299,7 +15648,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D11" s="123" t="s">
+      <c r="D11" s="122" t="s">
         <v>232</v>
       </c>
       <c r="E11" s="22"/>
@@ -15315,20 +15664,20 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="D13" s="22" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E13" s="22">
-        <f>'[1]Baseline Model Error'!B80^2</f>
-        <v>0.17414834807845733</v>
+        <f>'Baseline Model Error'!B80^2 + 'Project Model Error'!B89</f>
+        <v>0.17414834807849217</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="D14" s="22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E14" s="22">
         <f>SUM(E12:E13)</f>
-        <v>0.34294001546580699</v>
+        <v>0.34294001546584185</v>
       </c>
     </row>
   </sheetData>

--- a/Ecobliss_Results.xlsx
+++ b/Ecobliss_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mihirbendre/Documents/Gazelle/Gazelle_2025/Ghana_Project/QA1_&amp;_3/Code/RothC_Implementation_Ecobliss/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F952E342-A943-A743-BA41-7472EF3CA462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5211CE9-FE73-7548-89E7-F81BA4BED439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{AA4B684E-F9E2-7F41-996C-BD2AB92E0EF7}"/>
   </bookViews>
@@ -1420,11 +1420,11 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1788,19 +1788,19 @@
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="F3" s="125" t="s">
+      <c r="F3" s="124" t="s">
         <v>238</v>
       </c>
-      <c r="G3" s="125"/>
-      <c r="I3" s="125" t="s">
+      <c r="G3" s="124"/>
+      <c r="I3" s="124" t="s">
         <v>239</v>
       </c>
-      <c r="J3" s="125"/>
-      <c r="K3" s="125"/>
-      <c r="L3" s="125"/>
-      <c r="M3" s="125"/>
-      <c r="N3" s="125"/>
-      <c r="O3" s="125"/>
+      <c r="J3" s="124"/>
+      <c r="K3" s="124"/>
+      <c r="L3" s="124"/>
+      <c r="M3" s="124"/>
+      <c r="N3" s="124"/>
+      <c r="O3" s="124"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1966,9 +1966,12 @@
         <f>(N7+L7)-(I7+J7+K7+M7)</f>
         <v>-7197.487190219992</v>
       </c>
+      <c r="Q7">
+        <v>0.17499999999999999</v>
+      </c>
       <c r="T7" s="123">
-        <f>F7- G7 - O7</f>
-        <v>480486.80866484559</v>
+        <f>(F7- G7 - O7)*(1-Q7)</f>
+        <v>396401.61714849761</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
@@ -2016,9 +2019,12 @@
         <f t="shared" ref="O8:O18" si="2">(N8+L8)-(I8+J8+K8+M8)</f>
         <v>-7197.487190219992</v>
       </c>
+      <c r="Q8">
+        <v>0.17499999999999999</v>
+      </c>
       <c r="T8" s="123">
-        <f>F8-G8 - O8</f>
-        <v>465354.49413417903</v>
+        <f t="shared" ref="T8:T18" si="3">(F8- G8 - O8)*(1-Q8)</f>
+        <v>383917.45766069769</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
@@ -2066,9 +2072,12 @@
         <f t="shared" si="2"/>
         <v>-7197.487190219992</v>
       </c>
+      <c r="Q9">
+        <v>0.17499999999999999</v>
+      </c>
       <c r="T9" s="123">
-        <f>F9-G9 - O9</f>
-        <v>471934.05578951217</v>
+        <f t="shared" si="3"/>
+        <v>389345.59602634754</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
@@ -2116,9 +2125,12 @@
         <f t="shared" si="2"/>
         <v>-7197.487190219992</v>
       </c>
+      <c r="Q10">
+        <v>0.17499999999999999</v>
+      </c>
       <c r="T10" s="123">
-        <f>F10-G10 - O10</f>
-        <v>476726.02096751222</v>
+        <f t="shared" si="3"/>
+        <v>393298.96729819756</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
@@ -2166,9 +2178,12 @@
         <f t="shared" si="2"/>
         <v>-7197.487190219992</v>
       </c>
+      <c r="Q11">
+        <v>0.17499999999999999</v>
+      </c>
       <c r="T11" s="123">
-        <f>F11-G11 - O11</f>
-        <v>480232.16961351241</v>
+        <f t="shared" si="3"/>
+        <v>396191.53993114771</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
@@ -2216,9 +2231,12 @@
         <f t="shared" si="2"/>
         <v>-7197.487190219992</v>
       </c>
+      <c r="Q12">
+        <v>0.17499999999999999</v>
+      </c>
       <c r="T12" s="123">
-        <f>F12-G12 - O12</f>
-        <v>482812.33053017897</v>
+        <f t="shared" si="3"/>
+        <v>398320.17268739763</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.2">
@@ -2266,9 +2284,12 @@
         <f t="shared" si="2"/>
         <v>-7197.487190219992</v>
       </c>
+      <c r="Q13">
+        <v>0.17499999999999999</v>
+      </c>
       <c r="T13" s="123">
-        <f>F13-G13 - O13</f>
-        <v>484725.05534417898</v>
+        <f t="shared" si="3"/>
+        <v>399898.17065894767</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
@@ -2316,9 +2337,12 @@
         <f t="shared" si="2"/>
         <v>-7197.487190219992</v>
       </c>
+      <c r="Q14">
+        <v>0.17499999999999999</v>
+      </c>
       <c r="T14" s="123">
-        <f>F14-G14 - O14</f>
-        <v>486156.27246484556</v>
+        <f t="shared" si="3"/>
+        <v>401078.92478349758</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
@@ -2366,9 +2390,12 @@
         <f t="shared" si="2"/>
         <v>-7197.487190219992</v>
       </c>
+      <c r="Q15">
+        <v>0.17499999999999999</v>
+      </c>
       <c r="T15" s="123">
-        <f>F15-G15 - O15</f>
-        <v>487239.75019351236</v>
+        <f t="shared" si="3"/>
+        <v>401972.79390964768</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.2">
@@ -2416,9 +2443,12 @@
         <f t="shared" si="2"/>
         <v>-7197.487190219992</v>
       </c>
+      <c r="Q16">
+        <v>0.17499999999999999</v>
+      </c>
       <c r="T16" s="123">
-        <f>F16-G16 - O16</f>
-        <v>488071.80608484562</v>
+        <f t="shared" si="3"/>
+        <v>402659.24001999764</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.2">
@@ -2466,9 +2496,12 @@
         <f t="shared" si="2"/>
         <v>-7197.487190219992</v>
       </c>
+      <c r="Q17">
+        <v>0.17499999999999999</v>
+      </c>
       <c r="T17" s="123">
-        <f>F17-G17 - O17</f>
-        <v>488721.79409017897</v>
+        <f t="shared" si="3"/>
+        <v>403195.48012439761</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.2">
@@ -2516,9 +2549,12 @@
         <f t="shared" si="2"/>
         <v>-7197.487190219992</v>
       </c>
+      <c r="Q18">
+        <v>0.17499999999999999</v>
+      </c>
       <c r="T18" s="123">
-        <f>F18-G18 - O18</f>
-        <v>489239.67078284564</v>
+        <f t="shared" si="3"/>
+        <v>403622.72839584766</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.2">
@@ -12290,12 +12326,12 @@
       <c r="R85"/>
     </row>
     <row r="86" spans="1:44" ht="97" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="124" t="s">
+      <c r="B86" s="125" t="s">
         <v>218</v>
       </c>
-      <c r="C86" s="124"/>
-      <c r="D86" s="124"/>
-      <c r="E86" s="124"/>
+      <c r="C86" s="125"/>
+      <c r="D86" s="125"/>
+      <c r="E86" s="125"/>
       <c r="F86" s="121"/>
       <c r="G86" s="121"/>
       <c r="H86" s="121"/>
